--- a/data/availability/projects/hyde-park-developments/hyde-park-north-seashore.xlsx
+++ b/data/availability/projects/hyde-park-developments/hyde-park-north-seashore.xlsx
@@ -453,20 +453,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hyde Park</t>
+          <t>Hyde Park Developments</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Hyde Park North - Seashore</t>
+          <t>Live inventory for hyde-park-north-seashore</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,656 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>104</v>
+      </c>
+      <c r="F5" t="n">
+        <v>121</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>104</v>
+      </c>
+      <c r="F8" t="n">
+        <v>104</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="H8" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>135</v>
+      </c>
+      <c r="F9" t="n">
+        <v>135</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>112</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>127</v>
+      </c>
+      <c r="F11" t="n">
+        <v>138</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>65</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>182</v>
+      </c>
+      <c r="F13" t="n">
+        <v>182</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="H13" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Town Island - (HPN3)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>130</v>
+      </c>
+      <c r="F14" t="n">
+        <v>130</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Beach Chalet - HPN3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +1277,4520 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HPN4/WSB-19/G03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 56 sqm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>10400000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HPN4/WSA-20/G03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 97 sqm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>16790000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HPN4/WSA-5/G04</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 97 sqm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19250000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HPN4/WSB-12/G02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>65</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 49 sqm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>10220000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HPN4/WSB-13/G02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>65</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 49 sqm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>9660000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HPN4/WSA-17/G04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 97 sqm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>17880000</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HPN4/WSA-17/G05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Water Side</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 49 sqm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>9820000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-1/102</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>63</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>8060000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-2/103</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>67</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8930000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-3/203</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>9220000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-4/203</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>9470000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-3/301</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>119</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>15810000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-3/303</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>16120000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-4/303</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>121</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>16550000</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-5/301</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>119</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>15680000</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-5/303</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>121</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-1/402</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>62</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>8960000</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-5/401</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>104</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>16150000</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-1/403</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>104</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>15080000</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-3/503</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>87</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Floor: 5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>14520000</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-2/503</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>87</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Floor: 5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>14260000</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-3/G02</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>63</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 49 sqm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>10630000</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-4/G03</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>63</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 52 sqm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HPN4/WSC-5/G03</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Shore Residence</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>63</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Floor: 0 | Garden: 52 sqm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HPN3/SVB-55/G03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>76</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 47.2 sqm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>13090000</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HPN3/SVB-53/G02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>77</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 47.3 sqm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>13250000</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HPN3/SVB-52/G03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>76</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 47.2 sqm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>13030000</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HPN3/SVA-41/201</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>104</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>19470000</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HPN3/SVA-39/102</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Shorevill</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>135</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>22230000</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HPN5/LTC-57/203</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>112</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>14040000</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-56/301</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>138</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>18900000</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-56/206</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>110</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>15010000</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-56/101</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>130</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>16690000</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-53/301</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>138</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>16890000</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-53/101</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>130</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>15290000</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-53/G05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>79</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 58 sqm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>11990000</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HPN5/LTB-49/103</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>127</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>16180000</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HPN5/LTB-49/G03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>127</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 64.6 sqm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-48/306</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>138</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>17610000</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-48/301</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>110</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>14620000</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-48/206</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>130</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>16260000</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-34/504</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>80</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Floor: 5</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>9850000</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-34/405</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>80</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>9780000</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-34/206</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>110</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>13950000</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-47/306</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>110</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>14760000</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-47/101</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>130</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HPN5/LTB-46/201</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>112</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>14580000</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/402</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>80</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>9610000</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/401</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>65</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/306</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>138</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>16880000</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/302</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>79</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>9590000</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/301</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>110</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>14020000</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/101</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>110</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>13480000</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-44/G01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>106</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 38.7 sqm</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>14740000</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HPN5/LTB-43/G01</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>128</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 81.8 sqm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-42/405</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>80</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-42/301</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>138</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>16980000</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-42/106</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>110</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Floor: 1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>13560000</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-42/G05</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>79</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 58 sqm</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>12180000</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HPN5/LTB-25/201</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>112</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>13370000</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/406</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>65</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Floor: 4</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8480000</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/306</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>110</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Floor: 3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>12380000</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/202</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>80</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8410000</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/201</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>130</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>13770000</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/G06</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>106</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 38.7 sqm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>13320000</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-17/G03</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 75.6 sqm</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>13810000</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-9/504</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>79</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Floor: 5</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8960000</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-9/206</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>130</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Floor: 2</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>14580000</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-7/501</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>80</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Floor: 5</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>9070000</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HPN5/LTA-7/G04</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lagoon Town</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 75.6 sqm</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>14500000</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HPN3/6Plex/15E</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Town Island - (HPN3)</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>182</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Floor: None</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>34340000</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HPN3/7Plex/11G</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Town Island - (HPN3)</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>182</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Floor: None</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HPN3/6Plex/9F</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Town Island - (HPN3)</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>182</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Floor: None</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>39290000</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>hyde-park-north-seashore</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HPN3/BCB-22/G04</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Beach Chalet - HPN3</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>130</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Floor: None | Garden: 58.9 sqm</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>22450000</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/hyde-park-developments/hyde-park-north-seashore.xlsx
+++ b/data/availability/projects/hyde-park-developments/hyde-park-north-seashore.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Twin House with Roof</t>
+          <t>Twin House With Roof</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1459,7 +1459,6 @@
       <c r="G2" t="n">
         <v>65</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1470,7 +1469,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1516,7 +1515,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1527,7 +1525,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1573,7 +1571,6 @@
       <c r="G4" t="n">
         <v>65</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1584,7 +1581,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1630,7 +1627,6 @@
       <c r="G5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1641,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1687,7 +1683,6 @@
       <c r="G6" t="n">
         <v>65</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1698,7 +1693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1744,7 +1739,6 @@
       <c r="G7" t="n">
         <v>65</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1755,7 +1749,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1801,7 +1795,6 @@
       <c r="G8" t="n">
         <v>120</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1812,7 +1805,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1858,7 +1851,6 @@
       <c r="G9" t="n">
         <v>65</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1869,7 +1861,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1915,7 +1907,6 @@
       <c r="G10" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1926,7 +1917,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1972,7 +1963,6 @@
       <c r="G11" t="n">
         <v>65</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -1983,7 +1973,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2029,7 +2019,6 @@
       <c r="G12" t="n">
         <v>67</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2040,7 +2029,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2086,7 +2075,6 @@
       <c r="G13" t="n">
         <v>67</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2097,7 +2085,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2143,7 +2131,6 @@
       <c r="G14" t="n">
         <v>67</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2154,7 +2141,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2200,7 +2187,6 @@
       <c r="G15" t="n">
         <v>90</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2211,7 +2197,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2257,7 +2243,6 @@
       <c r="G16" t="n">
         <v>119</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2268,7 +2253,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2314,7 +2299,6 @@
       <c r="G17" t="n">
         <v>121</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2325,7 +2309,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2371,7 +2355,6 @@
       <c r="G18" t="n">
         <v>121</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2382,7 +2365,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2428,7 +2411,6 @@
       <c r="G19" t="n">
         <v>119</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2439,7 +2421,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2485,7 +2467,6 @@
       <c r="G20" t="n">
         <v>121</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2496,7 +2477,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2542,7 +2523,6 @@
       <c r="G21" t="n">
         <v>121</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2553,7 +2533,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2599,7 +2579,6 @@
       <c r="G22" t="n">
         <v>104</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2610,7 +2589,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2656,7 +2635,6 @@
       <c r="G23" t="n">
         <v>104</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2667,7 +2645,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2713,7 +2691,6 @@
       <c r="G24" t="n">
         <v>63</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2724,7 +2701,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2770,7 +2747,6 @@
       <c r="G25" t="n">
         <v>63</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2781,7 +2757,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2827,7 +2803,6 @@
       <c r="G26" t="n">
         <v>63</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2838,7 +2813,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2884,7 +2859,6 @@
       <c r="G27" t="n">
         <v>62</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2895,7 +2869,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2941,7 +2915,6 @@
       <c r="G28" t="n">
         <v>67</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -2952,7 +2925,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3013,7 +2986,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3074,7 +3047,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3135,7 +3108,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3196,7 +3169,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3257,7 +3230,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3318,7 +3291,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3379,7 +3352,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3440,7 +3413,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3501,7 +3474,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3523,7 +3496,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Twin House with Roof</t>
+          <t>Twin House With Roof</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3562,7 +3535,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3623,7 +3596,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3684,7 +3657,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3745,7 +3718,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3806,7 +3779,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3867,7 +3840,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3928,7 +3901,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3989,7 +3962,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4050,7 +4023,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4111,7 +4084,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4172,7 +4145,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4233,7 +4206,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4294,7 +4267,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4355,7 +4328,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4416,7 +4389,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4477,7 +4450,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4538,7 +4511,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4599,7 +4572,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4660,7 +4633,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4721,7 +4694,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4782,7 +4755,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4843,7 +4816,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4904,7 +4877,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4965,7 +4938,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5026,7 +4999,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5087,7 +5060,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5133,7 +5106,6 @@
       <c r="G64" t="n">
         <v>100</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5144,7 +5116,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5190,7 +5162,6 @@
       <c r="G65" t="n">
         <v>100</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5201,7 +5172,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5247,7 +5218,6 @@
       <c r="G66" t="n">
         <v>100</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5258,7 +5228,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5280,7 +5250,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Standard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5304,7 +5274,6 @@
       <c r="G67" t="n">
         <v>76.39118240000001</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5315,7 +5284,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5337,7 +5306,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Standard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5361,7 +5330,6 @@
       <c r="G68" t="n">
         <v>76.39118240000001</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5372,7 +5340,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5394,7 +5362,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Standard Chalet</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5418,7 +5386,6 @@
       <c r="G69" t="n">
         <v>135.7049099</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5429,7 +5396,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5475,7 +5442,6 @@
       <c r="G70" t="n">
         <v>112</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5486,7 +5452,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5532,7 +5498,6 @@
       <c r="G71" t="n">
         <v>110</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5543,7 +5508,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5589,7 +5554,6 @@
       <c r="G72" t="n">
         <v>138</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5600,7 +5564,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5646,7 +5610,6 @@
       <c r="G73" t="n">
         <v>79</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5657,7 +5620,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5703,7 +5666,6 @@
       <c r="G74" t="n">
         <v>138</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5714,7 +5676,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5760,7 +5722,6 @@
       <c r="G75" t="n">
         <v>127</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5771,7 +5732,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5817,7 +5778,6 @@
       <c r="G76" t="n">
         <v>127</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5828,7 +5788,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5874,7 +5834,6 @@
       <c r="G77" t="n">
         <v>138</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5885,7 +5844,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5931,7 +5890,6 @@
       <c r="G78" t="n">
         <v>100</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5942,7 +5900,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5988,7 +5946,6 @@
       <c r="G79" t="n">
         <v>130</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5999,7 +5956,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6045,7 +6002,6 @@
       <c r="G80" t="n">
         <v>138</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6056,7 +6012,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6102,7 +6058,6 @@
       <c r="G81" t="n">
         <v>80</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6113,7 +6068,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6159,7 +6114,6 @@
       <c r="G82" t="n">
         <v>110</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6170,7 +6124,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6216,7 +6170,6 @@
       <c r="G83" t="n">
         <v>110</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6227,7 +6180,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6273,7 +6226,6 @@
       <c r="G84" t="n">
         <v>110</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6284,7 +6236,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6330,7 +6282,6 @@
       <c r="G85" t="n">
         <v>130</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6341,7 +6292,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6387,7 +6338,6 @@
       <c r="G86" t="n">
         <v>112</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6398,7 +6348,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6444,7 +6394,6 @@
       <c r="G87" t="n">
         <v>127</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6455,7 +6404,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6501,7 +6450,6 @@
       <c r="G88" t="n">
         <v>128</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6512,7 +6460,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6558,7 +6506,6 @@
       <c r="G89" t="n">
         <v>80</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6569,7 +6516,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6615,7 +6562,6 @@
       <c r="G90" t="n">
         <v>65</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6626,7 +6572,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6672,7 +6618,6 @@
       <c r="G91" t="n">
         <v>138</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6683,7 +6628,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6729,7 +6674,6 @@
       <c r="G92" t="n">
         <v>79</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6740,7 +6684,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6786,7 +6730,6 @@
       <c r="G93" t="n">
         <v>110</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6797,7 +6740,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6843,7 +6786,6 @@
       <c r="G94" t="n">
         <v>79</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6854,7 +6796,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6900,7 +6842,6 @@
       <c r="G95" t="n">
         <v>110</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6911,7 +6852,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6957,7 +6898,6 @@
       <c r="G96" t="n">
         <v>128</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6968,7 +6908,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7014,7 +6954,6 @@
       <c r="G97" t="n">
         <v>80</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7025,7 +6964,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7071,7 +7010,6 @@
       <c r="G98" t="n">
         <v>80</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7082,7 +7020,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7128,7 +7066,6 @@
       <c r="G99" t="n">
         <v>110</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7139,7 +7076,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7185,7 +7122,6 @@
       <c r="G100" t="n">
         <v>79</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7196,7 +7132,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7242,7 +7178,6 @@
       <c r="G101" t="n">
         <v>138</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7253,7 +7188,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7299,7 +7234,6 @@
       <c r="G102" t="n">
         <v>110</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7310,7 +7244,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7356,7 +7290,6 @@
       <c r="G103" t="n">
         <v>110</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7367,7 +7300,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7413,7 +7346,6 @@
       <c r="G104" t="n">
         <v>79</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7424,7 +7356,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7470,7 +7402,6 @@
       <c r="G105" t="n">
         <v>130</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7481,7 +7412,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7527,7 +7458,6 @@
       <c r="G106" t="n">
         <v>79</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7538,7 +7468,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7584,7 +7514,6 @@
       <c r="G107" t="n">
         <v>73</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7595,7 +7524,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7641,7 +7570,6 @@
       <c r="G108" t="n">
         <v>138</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7652,7 +7580,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7698,7 +7626,6 @@
       <c r="G109" t="n">
         <v>112</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7709,7 +7636,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7755,7 +7682,6 @@
       <c r="G110" t="n">
         <v>80</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7766,7 +7692,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7812,7 +7738,6 @@
       <c r="G111" t="n">
         <v>96</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7823,7 +7748,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7869,7 +7794,6 @@
       <c r="G112" t="n">
         <v>112</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7880,7 +7804,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7926,7 +7850,6 @@
       <c r="G113" t="n">
         <v>79</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7937,7 +7860,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7983,7 +7906,6 @@
       <c r="G114" t="n">
         <v>80</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7994,7 +7916,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8040,7 +7962,6 @@
       <c r="G115" t="n">
         <v>110</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8051,7 +7972,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8097,7 +8018,6 @@
       <c r="G116" t="n">
         <v>65</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8108,7 +8028,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8154,7 +8074,6 @@
       <c r="G117" t="n">
         <v>79</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8165,7 +8084,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8211,7 +8130,6 @@
       <c r="G118" t="n">
         <v>110</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8222,7 +8140,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8268,7 +8186,6 @@
       <c r="G119" t="n">
         <v>138</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8279,7 +8196,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8325,7 +8242,6 @@
       <c r="G120" t="n">
         <v>79</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8336,7 +8252,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8382,7 +8298,6 @@
       <c r="G121" t="n">
         <v>80</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8393,7 +8308,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8439,7 +8354,6 @@
       <c r="G122" t="n">
         <v>65</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8450,7 +8364,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8496,7 +8410,6 @@
       <c r="G123" t="n">
         <v>66</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8507,7 +8420,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8553,7 +8466,6 @@
       <c r="G124" t="n">
         <v>112</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8564,7 +8476,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8610,7 +8522,6 @@
       <c r="G125" t="n">
         <v>65</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8621,7 +8532,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8667,7 +8578,6 @@
       <c r="G126" t="n">
         <v>110</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8678,7 +8588,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8724,7 +8634,6 @@
       <c r="G127" t="n">
         <v>130</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8735,7 +8644,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8781,7 +8690,6 @@
       <c r="G128" t="n">
         <v>73</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8792,7 +8700,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8838,7 +8746,6 @@
       <c r="G129" t="n">
         <v>100</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8849,7 +8756,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8895,7 +8802,6 @@
       <c r="G130" t="n">
         <v>100</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8906,7 +8812,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8952,7 +8858,6 @@
       <c r="G131" t="n">
         <v>100</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8963,7 +8868,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9009,7 +8914,6 @@
       <c r="G132" t="n">
         <v>100</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9020,7 +8924,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9066,7 +8970,6 @@
       <c r="G133" t="n">
         <v>100</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9077,7 +8980,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9123,7 +9026,6 @@
       <c r="G134" t="n">
         <v>96</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9134,7 +9036,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9180,7 +9082,6 @@
       <c r="G135" t="n">
         <v>130</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9191,7 +9092,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9252,7 +9153,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9313,7 +9214,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9374,7 +9275,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
